--- a/docs/entregables/SEM02/cronograma.xlsx
+++ b/docs/entregables/SEM02/cronograma.xlsx
@@ -18922,7 +18922,7 @@
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>Sistema Web Integral 100%</t>
+          <t>Sistema Web Integral Consolidado</t>
         </is>
       </c>
       <c r="C89" s="17" t="n"/>
